--- a/data/holidays/school_holidays.xlsx
+++ b/data/holidays/school_holidays.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iftek\Documents\MPI\mobility inference\mobility_inference\data\holidays\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40001_{83A81902-8021-4C95-8B00-2DA49AC335E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8ABC9D-FE8D-44D8-9AFC-95A1D3B475CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022" sheetId="1" r:id="rId1"/>
-    <sheet name="2020" sheetId="2" r:id="rId2"/>
+    <sheet name="2021" sheetId="4" r:id="rId2"/>
+    <sheet name="2020" sheetId="2" r:id="rId3"/>
+    <sheet name="2019" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="224">
   <si>
     <t>Bundesland</t>
   </si>
@@ -328,12 +330,393 @@
   </si>
   <si>
     <t>17.10 - 30.10</t>
+  </si>
+  <si>
+    <t>Winterferien</t>
+  </si>
+  <si>
+    <t>Weihnachtsferien</t>
+  </si>
+  <si>
+    <t>15.04 - 27.04</t>
+  </si>
+  <si>
+    <t>11.06 - 21.06</t>
+  </si>
+  <si>
+    <t>29.07 - 10.09</t>
+  </si>
+  <si>
+    <t>28.10 - 30.10</t>
+  </si>
+  <si>
+    <t>23.12 - 04.01</t>
+  </si>
+  <si>
+    <t>04.03 - 08.03</t>
+  </si>
+  <si>
+    <t>29.07 - 09.09</t>
+  </si>
+  <si>
+    <t>28.10 - 31.10, 20.11</t>
+  </si>
+  <si>
+    <t>04.02 - 09.02</t>
+  </si>
+  <si>
+    <t>15.04 - 26.04</t>
+  </si>
+  <si>
+    <t>31.05, 11.06</t>
+  </si>
+  <si>
+    <t>20.06 - 02.08</t>
+  </si>
+  <si>
+    <t>04.10, 07.10 - 19.10</t>
+  </si>
+  <si>
+    <t>20.06 - 03.08</t>
+  </si>
+  <si>
+    <t>04.10 - 18.10</t>
+  </si>
+  <si>
+    <t>23.12 - 03.01</t>
+  </si>
+  <si>
+    <t>31.01 - 01.02</t>
+  </si>
+  <si>
+    <t>06.04 - 23.04</t>
+  </si>
+  <si>
+    <t>04.07 - 14.08</t>
+  </si>
+  <si>
+    <t>21.12 - 06.01</t>
+  </si>
+  <si>
+    <t>04.03 - 15.03</t>
+  </si>
+  <si>
+    <t>13.05 - 17.05, 31.05</t>
+  </si>
+  <si>
+    <t>27.06 - 07.08</t>
+  </si>
+  <si>
+    <t>20.12 - 03.01</t>
+  </si>
+  <si>
+    <t>14.04 - 27.04</t>
+  </si>
+  <si>
+    <t>01.07 - 09.08</t>
+  </si>
+  <si>
+    <t>30.09 - 12.10</t>
+  </si>
+  <si>
+    <t>23.12 - 11.01</t>
+  </si>
+  <si>
+    <t>04.02 - 15.02</t>
+  </si>
+  <si>
+    <t>15.04 - 24.04</t>
+  </si>
+  <si>
+    <t>22.05, 07.06 - 11.06</t>
+  </si>
+  <si>
+    <t>01.07 - 10.08</t>
+  </si>
+  <si>
+    <t>04.10, 07.10 - 12.10, 01.11</t>
+  </si>
+  <si>
+    <t>08.04 - 23.04</t>
+  </si>
+  <si>
+    <t>23.12 - 06.01</t>
+  </si>
+  <si>
+    <t>15.07 - 27.08</t>
+  </si>
+  <si>
+    <t>14.10 - 26.10</t>
+  </si>
+  <si>
+    <t>25.02 - 01.03</t>
+  </si>
+  <si>
+    <t>23.04 - 30.04</t>
+  </si>
+  <si>
+    <t>30.09 - 11.10</t>
+  </si>
+  <si>
+    <t>25.02 - 05.03</t>
+  </si>
+  <si>
+    <t>17.04 - 26.04</t>
+  </si>
+  <si>
+    <t>07.10 - 18.10</t>
+  </si>
+  <si>
+    <t>18.02 - 02.03</t>
+  </si>
+  <si>
+    <t>19.04 - 26.04</t>
+  </si>
+  <si>
+    <t>08.07 - 16.08</t>
+  </si>
+  <si>
+    <t>14.10 - 25.10</t>
+  </si>
+  <si>
+    <t>21.12 - 03.01</t>
+  </si>
+  <si>
+    <t>11.02 - 15.02</t>
+  </si>
+  <si>
+    <t>18.04 - 30.04</t>
+  </si>
+  <si>
+    <t>31.05 - 01.06</t>
+  </si>
+  <si>
+    <t>04.10 - 11.10, 01.11</t>
+  </si>
+  <si>
+    <t>04.04 - 18.04</t>
+  </si>
+  <si>
+    <t>08.07 - 17.08</t>
+  </si>
+  <si>
+    <t>07.10 - 19.10</t>
+  </si>
+  <si>
+    <t>24.02 - 28.02</t>
+  </si>
+  <si>
+    <t>03.02 - 08.02</t>
+  </si>
+  <si>
+    <t>03.02 - 04.02</t>
+  </si>
+  <si>
+    <t>10.02 - 21.02</t>
+  </si>
+  <si>
+    <t>17.02 - 21.02</t>
+  </si>
+  <si>
+    <t>17.02 - 25.02</t>
+  </si>
+  <si>
+    <t>10.02 - 22.02</t>
+  </si>
+  <si>
+    <t>10.02 - 14.02</t>
+  </si>
+  <si>
+    <t>01.04, 06.04 - 10.04</t>
+  </si>
+  <si>
+    <t>25.05 - 05.06</t>
+  </si>
+  <si>
+    <t>29.07 - 11.09</t>
+  </si>
+  <si>
+    <t>31.10, 02.11 - 06.11</t>
+  </si>
+  <si>
+    <t>23.12 - 08.01</t>
+  </si>
+  <si>
+    <t>15.02 - 19.02</t>
+  </si>
+  <si>
+    <t>29.03 - 10.04</t>
+  </si>
+  <si>
+    <t>25.05 - 04.06</t>
+  </si>
+  <si>
+    <t>30.07 - 13.09</t>
+  </si>
+  <si>
+    <t>02.11 - 05.11, 17.11</t>
+  </si>
+  <si>
+    <t>24.12 - 08.01</t>
+  </si>
+  <si>
+    <t>01.02 - 06.02</t>
+  </si>
+  <si>
+    <t>24.06 - 06.08</t>
+  </si>
+  <si>
+    <t>11.10 - 23.10</t>
+  </si>
+  <si>
+    <t>24.12 - 31.12</t>
+  </si>
+  <si>
+    <t>29.03 - 09.04</t>
+  </si>
+  <si>
+    <t>24.06 - 07.08</t>
+  </si>
+  <si>
+    <t>23.12 - 31.12</t>
+  </si>
+  <si>
+    <t>01.02 - 02.02</t>
+  </si>
+  <si>
+    <t>27.03 - 10.04</t>
+  </si>
+  <si>
+    <t>14.05, 25.05</t>
+  </si>
+  <si>
+    <t>22.07 - 01.09</t>
+  </si>
+  <si>
+    <t>18.10 - 30.10</t>
+  </si>
+  <si>
+    <t>01.03 - 12.03</t>
+  </si>
+  <si>
+    <t>10.05 - 14.05</t>
+  </si>
+  <si>
+    <t>24.06 - 04.08</t>
+  </si>
+  <si>
+    <t>06.04 - 16.04</t>
+  </si>
+  <si>
+    <t>19.07 - 27.08</t>
+  </si>
+  <si>
+    <t>06.02 - 18.02, 19.02</t>
+  </si>
+  <si>
+    <t>29.03 - 07.04</t>
+  </si>
+  <si>
+    <t>14.05, 21.05 - 25.05</t>
+  </si>
+  <si>
+    <t>21.06 - 31.07</t>
+  </si>
+  <si>
+    <t>05.10 - 10.10, 02.11 - 03.11</t>
+  </si>
+  <si>
+    <t>22.12 - 31.12</t>
+  </si>
+  <si>
+    <t>18.10 - 29.10</t>
+  </si>
+  <si>
+    <t>23.12 - 07.01</t>
+  </si>
+  <si>
+    <t>05.07 - 17.08</t>
+  </si>
+  <si>
+    <t>29.03 - 06.04</t>
+  </si>
+  <si>
+    <t>25.05 - 02.06</t>
+  </si>
+  <si>
+    <t>11.10 - 22.10</t>
+  </si>
+  <si>
+    <t>25.05 - 28.05</t>
+  </si>
+  <si>
+    <t>08.02 - 20.02</t>
+  </si>
+  <si>
+    <t>02.04 - 10.04</t>
+  </si>
+  <si>
+    <t>26.07 - 03.09</t>
+  </si>
+  <si>
+    <t>23.12 - 01.01</t>
+  </si>
+  <si>
+    <t>08.02 - 13.02</t>
+  </si>
+  <si>
+    <t>29.03 - 03.04</t>
+  </si>
+  <si>
+    <t>10.05 - 22.05</t>
+  </si>
+  <si>
+    <t>25.10 - 30.10</t>
+  </si>
+  <si>
+    <t>22.12 - 08.01</t>
+  </si>
+  <si>
+    <t>01.04 - 16.04</t>
+  </si>
+  <si>
+    <t>14.05 - 15.05</t>
+  </si>
+  <si>
+    <t>04.10 - 16.10</t>
+  </si>
+  <si>
+    <t>26.07 - 04.09</t>
+  </si>
+  <si>
+    <t>25.10 - 06.11</t>
+  </si>
+  <si>
+    <t>23.12 - 09.01</t>
+  </si>
+  <si>
+    <t>21.12 - 02.01</t>
+  </si>
+  <si>
+    <t>21.12 - 04.01</t>
+  </si>
+  <si>
+    <t>21.12 - 09.01</t>
+  </si>
+  <si>
+    <t>21.12 - 31.12</t>
+  </si>
+  <si>
+    <t>23.12 - 02.01</t>
+  </si>
+  <si>
+    <t>21.12 - 05.01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -756,7 +1139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
@@ -1043,339 +1426,1255 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1" display="https://www.ferienwiki.de/ferientermine/2022/de/osterferien"/>
-    <hyperlink ref="C1" r:id="rId2" display="https://www.ferienwiki.de/ferientermine/2022/de/pfingstferien"/>
-    <hyperlink ref="D1" r:id="rId3" display="https://www.ferienwiki.de/ferientermine/2022/de/sommerferien"/>
-    <hyperlink ref="E1" r:id="rId4" display="https://www.ferienwiki.de/ferientermine/2022/de/herbstferien"/>
-    <hyperlink ref="A2" r:id="rId5" display="https://www.ferienwiki.de/ferientermine/de/baden-wuerttemberg"/>
-    <hyperlink ref="A3" r:id="rId6" display="https://www.ferienwiki.de/ferientermine/de/bayern"/>
-    <hyperlink ref="A4" r:id="rId7" display="https://www.ferienwiki.de/ferientermine/de/berlin"/>
-    <hyperlink ref="A5" r:id="rId8" display="https://www.ferienwiki.de/ferientermine/de/brandenburg"/>
-    <hyperlink ref="A6" r:id="rId9" display="https://www.ferienwiki.de/ferientermine/de/bremen"/>
-    <hyperlink ref="A7" r:id="rId10" display="https://www.ferienwiki.de/ferientermine/de/hamburg"/>
-    <hyperlink ref="A8" r:id="rId11" display="https://www.ferienwiki.de/ferientermine/de/hessen"/>
-    <hyperlink ref="A9" r:id="rId12" display="https://www.ferienwiki.de/ferientermine/de/mecklenburg-vorpommern"/>
-    <hyperlink ref="A10" r:id="rId13" display="https://www.ferienwiki.de/ferientermine/de/niedersachsen"/>
-    <hyperlink ref="A11" r:id="rId14" display="https://www.ferienwiki.de/ferientermine/de/nordrhein-westfalen"/>
-    <hyperlink ref="A12" r:id="rId15" display="https://www.ferienwiki.de/ferientermine/de/rheinland-pfalz"/>
-    <hyperlink ref="A13" r:id="rId16" display="https://www.ferienwiki.de/ferientermine/de/saarland"/>
-    <hyperlink ref="A14" r:id="rId17" display="https://www.ferienwiki.de/ferientermine/de/sachsen"/>
-    <hyperlink ref="A15" r:id="rId18" display="https://www.ferienwiki.de/ferientermine/de/sachsen-anhalt"/>
-    <hyperlink ref="A16" r:id="rId19" display="https://www.ferienwiki.de/ferientermine/de/schleswig-holstein"/>
-    <hyperlink ref="A17" r:id="rId20" display="https://www.ferienwiki.de/ferientermine/de/thueringen"/>
+    <hyperlink ref="B1" r:id="rId1" display="https://www.ferienwiki.de/ferientermine/2022/de/osterferien" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C1" r:id="rId2" display="https://www.ferienwiki.de/ferientermine/2022/de/pfingstferien" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D1" r:id="rId3" display="https://www.ferienwiki.de/ferientermine/2022/de/sommerferien" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E1" r:id="rId4" display="https://www.ferienwiki.de/ferientermine/2022/de/herbstferien" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A2" r:id="rId5" display="https://www.ferienwiki.de/ferientermine/de/baden-wuerttemberg" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A3" r:id="rId6" display="https://www.ferienwiki.de/ferientermine/de/bayern" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A4" r:id="rId7" display="https://www.ferienwiki.de/ferientermine/de/berlin" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A5" r:id="rId8" display="https://www.ferienwiki.de/ferientermine/de/brandenburg" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A6" r:id="rId9" display="https://www.ferienwiki.de/ferientermine/de/bremen" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="A7" r:id="rId10" display="https://www.ferienwiki.de/ferientermine/de/hamburg" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A8" r:id="rId11" display="https://www.ferienwiki.de/ferientermine/de/hessen" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A9" r:id="rId12" display="https://www.ferienwiki.de/ferientermine/de/mecklenburg-vorpommern" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A10" r:id="rId13" display="https://www.ferienwiki.de/ferientermine/de/niedersachsen" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A11" r:id="rId14" display="https://www.ferienwiki.de/ferientermine/de/nordrhein-westfalen" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A12" r:id="rId15" display="https://www.ferienwiki.de/ferientermine/de/rheinland-pfalz" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A13" r:id="rId16" display="https://www.ferienwiki.de/ferientermine/de/saarland" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A14" r:id="rId17" display="https://www.ferienwiki.de/ferientermine/de/sachsen" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="A15" r:id="rId18" display="https://www.ferienwiki.de/ferientermine/de/sachsen-anhalt" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="A16" r:id="rId19" display="https://www.ferienwiki.de/ferientermine/de/schleswig-holstein" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="A17" r:id="rId20" display="https://www.ferienwiki.de/ferientermine/de/thueringen" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF52838E-05E9-46C2-AF86-524833A1A2AF}">
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1">
+    <row r="1" spans="1:7" ht="29.4" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.8" thickBot="1">
+      <c r="G1" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="43.8" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.4" thickBot="1">
+        <v>164</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="23.4" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1">
+        <v>170</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>66</v>
+        <v>173</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>68</v>
+        <v>168</v>
+      </c>
+      <c r="D4" s="4">
+        <v>14.05</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1">
+        <v>174</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1">
+        <v>178</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="4">
-        <v>22.05</v>
+        <v>180</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1">
+        <v>183</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1">
       <c r="A7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>73</v>
+      <c r="B7" s="6">
+        <v>29.01</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1">
+        <v>187</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1">
       <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
-        <v>77</v>
-      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="43.8" thickBot="1">
+        <v>189</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.8" thickBot="1">
       <c r="A9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="6">
-        <v>22.05</v>
+        <v>190</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="29.4" thickBot="1">
+        <v>193</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29.4" thickBot="1">
       <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="4">
-        <v>22.05</v>
+        <v>180</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="29.4" thickBot="1">
+        <v>183</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="29.4" thickBot="1">
       <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2.06</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>84</v>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="6">
+        <v>25.05</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="29.4" thickBot="1">
+        <v>198</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29.4" thickBot="1">
       <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
+        <v>199</v>
+      </c>
       <c r="D12" s="4" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1">
+        <v>189</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1">
       <c r="A13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="6"/>
+        <v>167</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="D13" s="6" t="s">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1">
+        <v>189</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1">
       <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="4">
-        <v>22.05</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>88</v>
+        <v>203</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="4">
+        <v>14.05</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="29.4" thickBot="1">
+        <v>205</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29.4" thickBot="1">
       <c r="A15" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>91</v>
+        <v>208</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="29.4" thickBot="1">
+        <v>183</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29.4" thickBot="1">
       <c r="A16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="4">
-        <v>22.05</v>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1">
+        <v>193</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1">
       <c r="A17" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="8">
-        <v>22.05</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>95</v>
+        <v>207</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="8">
+        <v>14.05</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>96</v>
+        <v>215</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1" display="https://www.ferienwiki.de/ferientermine/2020/de/osterferien"/>
-    <hyperlink ref="C1" r:id="rId2" display="https://www.ferienwiki.de/ferientermine/2020/de/pfingstferien"/>
-    <hyperlink ref="D1" r:id="rId3" display="https://www.ferienwiki.de/ferientermine/2020/de/sommerferien"/>
-    <hyperlink ref="E1" r:id="rId4" display="https://www.ferienwiki.de/ferientermine/2020/de/herbstferien"/>
-    <hyperlink ref="A2" r:id="rId5" display="https://www.ferienwiki.de/ferientermine/de/baden-wuerttemberg"/>
-    <hyperlink ref="A3" r:id="rId6" display="https://www.ferienwiki.de/ferientermine/de/bayern"/>
-    <hyperlink ref="A4" r:id="rId7" display="https://www.ferienwiki.de/ferientermine/de/berlin"/>
-    <hyperlink ref="A5" r:id="rId8" display="https://www.ferienwiki.de/ferientermine/de/brandenburg"/>
-    <hyperlink ref="A6" r:id="rId9" display="https://www.ferienwiki.de/ferientermine/de/bremen"/>
-    <hyperlink ref="A7" r:id="rId10" display="https://www.ferienwiki.de/ferientermine/de/hamburg"/>
-    <hyperlink ref="A8" r:id="rId11" display="https://www.ferienwiki.de/ferientermine/de/hessen"/>
-    <hyperlink ref="A9" r:id="rId12" display="https://www.ferienwiki.de/ferientermine/de/mecklenburg-vorpommern"/>
-    <hyperlink ref="A10" r:id="rId13" display="https://www.ferienwiki.de/ferientermine/de/niedersachsen"/>
-    <hyperlink ref="A11" r:id="rId14" display="https://www.ferienwiki.de/ferientermine/de/nordrhein-westfalen"/>
-    <hyperlink ref="A12" r:id="rId15" display="https://www.ferienwiki.de/ferientermine/de/rheinland-pfalz"/>
-    <hyperlink ref="A13" r:id="rId16" display="https://www.ferienwiki.de/ferientermine/de/saarland"/>
-    <hyperlink ref="A14" r:id="rId17" display="https://www.ferienwiki.de/ferientermine/de/sachsen"/>
-    <hyperlink ref="A15" r:id="rId18" display="https://www.ferienwiki.de/ferientermine/de/sachsen-anhalt"/>
-    <hyperlink ref="A16" r:id="rId19" display="https://www.ferienwiki.de/ferientermine/de/schleswig-holstein"/>
-    <hyperlink ref="A17" r:id="rId20" display="https://www.ferienwiki.de/ferientermine/de/thueringen"/>
+    <hyperlink ref="B1" r:id="rId1" display="https://www.ferienwiki.de/ferientermine/2021/de/winterferien" xr:uid="{09D76223-BCAE-4582-B68A-A69D0F71F50A}"/>
+    <hyperlink ref="C1" r:id="rId2" display="https://www.ferienwiki.de/ferientermine/2021/de/osterferien" xr:uid="{4C8B729F-C01D-43F8-B5B5-83C87941800C}"/>
+    <hyperlink ref="D1" r:id="rId3" display="https://www.ferienwiki.de/ferientermine/2021/de/pfingstferien" xr:uid="{B1D93808-2757-40C5-A411-743BE1C20730}"/>
+    <hyperlink ref="E1" r:id="rId4" display="https://www.ferienwiki.de/ferientermine/2021/de/sommerferien" xr:uid="{3B127D63-98A3-4E0D-B588-E2400A91FBF6}"/>
+    <hyperlink ref="F1" r:id="rId5" display="https://www.ferienwiki.de/ferientermine/2021/de/herbstferien" xr:uid="{DD1E3A1A-5CD7-476A-9682-50491A797768}"/>
+    <hyperlink ref="G1" r:id="rId6" display="https://www.ferienwiki.de/ferientermine/2021/de/weihnachtsferien" xr:uid="{B68B41DA-9F34-4507-BB53-BF3B4AF81021}"/>
+    <hyperlink ref="A2" r:id="rId7" display="https://www.ferienwiki.de/ferientermine/de/baden-wuerttemberg" xr:uid="{741E8E86-C45A-4298-9FFB-E519826384C9}"/>
+    <hyperlink ref="A3" r:id="rId8" display="https://www.ferienwiki.de/ferientermine/de/bayern" xr:uid="{5E17981F-A094-473E-81CC-052E885718FE}"/>
+    <hyperlink ref="A4" r:id="rId9" display="https://www.ferienwiki.de/ferientermine/de/berlin" xr:uid="{2C9E6975-964F-4B0F-955D-EC7F51D09415}"/>
+    <hyperlink ref="A5" r:id="rId10" display="https://www.ferienwiki.de/ferientermine/de/brandenburg" xr:uid="{70278199-ACBA-4CCC-8816-1023F42C1D53}"/>
+    <hyperlink ref="A6" r:id="rId11" display="https://www.ferienwiki.de/ferientermine/de/bremen" xr:uid="{3897D4A7-8FAB-4F81-9441-E76628F3239C}"/>
+    <hyperlink ref="A7" r:id="rId12" display="https://www.ferienwiki.de/ferientermine/de/hamburg" xr:uid="{11DF673F-9E00-4EFB-978D-E3862C3E39D7}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://www.ferienwiki.de/ferientermine/de/hessen" xr:uid="{CE2498BA-5E4F-4232-AF0D-9AD96CE6D3DA}"/>
+    <hyperlink ref="A9" r:id="rId14" display="https://www.ferienwiki.de/ferientermine/de/mecklenburg-vorpommern" xr:uid="{82739084-E2CF-4635-BAE1-95F20DA6EA1D}"/>
+    <hyperlink ref="A10" r:id="rId15" display="https://www.ferienwiki.de/ferientermine/de/niedersachsen" xr:uid="{117CE84E-F4C4-4F67-AEEC-8DBD39E153D2}"/>
+    <hyperlink ref="A11" r:id="rId16" display="https://www.ferienwiki.de/ferientermine/de/nordrhein-westfalen" xr:uid="{9EFCF3C9-A4EC-404E-9FA9-89B7CBA9D8E3}"/>
+    <hyperlink ref="A12" r:id="rId17" display="https://www.ferienwiki.de/ferientermine/de/rheinland-pfalz" xr:uid="{50388C19-3938-4BAD-A200-3D0C2539A9AA}"/>
+    <hyperlink ref="A13" r:id="rId18" display="https://www.ferienwiki.de/ferientermine/de/saarland" xr:uid="{D445B58F-8139-4EBD-91CB-D4FAA39FE238}"/>
+    <hyperlink ref="A14" r:id="rId19" display="https://www.ferienwiki.de/ferientermine/de/sachsen" xr:uid="{D16D7F5B-D137-411C-83C5-54A3DF4A0AED}"/>
+    <hyperlink ref="A15" r:id="rId20" display="https://www.ferienwiki.de/ferientermine/de/sachsen-anhalt" xr:uid="{58045A3D-F3E4-4E08-AA7E-105F0AED39B3}"/>
+    <hyperlink ref="A16" r:id="rId21" display="https://www.ferienwiki.de/ferientermine/de/schleswig-holstein" xr:uid="{FEF1C87F-323C-477C-8A3B-D20195BE2E63}"/>
+    <hyperlink ref="A17" r:id="rId22" display="https://www.ferienwiki.de/ferientermine/de/thueringen" xr:uid="{3F41029E-EC46-4C51-B04C-C32002F54007}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="43.8" thickBot="1">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="23.4" thickBot="1">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1">
+      <c r="A5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="4">
+        <v>22.05</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="6">
+        <v>31.01</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1">
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.8" thickBot="1">
+      <c r="A9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="6">
+        <v>22.05</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="4">
+        <v>22.05</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2.06</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1">
+      <c r="A13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1">
+      <c r="A14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="4">
+        <v>22.05</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="4">
+        <v>22.05</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1">
+      <c r="A17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="8">
+        <v>22.05</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B1" r:id="rId1" display="https://www.ferienwiki.de/ferientermine/2020/de/winterferien" xr:uid="{24E2A993-9C40-438C-959C-C2431AE0744D}"/>
+    <hyperlink ref="C1" r:id="rId2" display="https://www.ferienwiki.de/ferientermine/2020/de/osterferien" xr:uid="{E58F8DFD-6ACB-467E-9976-8F37C2510ED2}"/>
+    <hyperlink ref="D1" r:id="rId3" display="https://www.ferienwiki.de/ferientermine/2020/de/pfingstferien" xr:uid="{8F08C0B4-5BBA-4CE0-BE57-13D7AB5EF09A}"/>
+    <hyperlink ref="E1" r:id="rId4" display="https://www.ferienwiki.de/ferientermine/2020/de/sommerferien" xr:uid="{3C89BA2F-C0BA-4606-9994-38D193D5EFC0}"/>
+    <hyperlink ref="F1" r:id="rId5" display="https://www.ferienwiki.de/ferientermine/2020/de/herbstferien" xr:uid="{106827CB-7357-44A3-B777-B68430264215}"/>
+    <hyperlink ref="G1" r:id="rId6" display="https://www.ferienwiki.de/ferientermine/2020/de/weihnachtsferien" xr:uid="{3EC5D63C-B9FA-49AF-BFB5-6C17E7539F09}"/>
+    <hyperlink ref="A2" r:id="rId7" display="https://www.ferienwiki.de/ferientermine/de/baden-wuerttemberg" xr:uid="{133019D7-B37E-4D24-9BA3-0040C068467C}"/>
+    <hyperlink ref="A3" r:id="rId8" display="https://www.ferienwiki.de/ferientermine/de/bayern" xr:uid="{DA6293F6-19D8-414C-9506-7AA0A30C4F0E}"/>
+    <hyperlink ref="A4" r:id="rId9" display="https://www.ferienwiki.de/ferientermine/de/berlin" xr:uid="{EE12BF95-5AD4-462D-B1D4-C49713A03FF1}"/>
+    <hyperlink ref="A5" r:id="rId10" display="https://www.ferienwiki.de/ferientermine/de/brandenburg" xr:uid="{9DC01E63-868D-4063-988E-899D9C539EB0}"/>
+    <hyperlink ref="A6" r:id="rId11" display="https://www.ferienwiki.de/ferientermine/de/bremen" xr:uid="{6B5F2DC5-DA05-430F-9D74-E67DDED51D39}"/>
+    <hyperlink ref="A7" r:id="rId12" display="https://www.ferienwiki.de/ferientermine/de/hamburg" xr:uid="{718B1B74-C5F7-4FAF-91E9-45C8B987C979}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://www.ferienwiki.de/ferientermine/de/hessen" xr:uid="{8493A2CC-DECD-40EB-AFBB-9FAC579702AA}"/>
+    <hyperlink ref="A9" r:id="rId14" display="https://www.ferienwiki.de/ferientermine/de/mecklenburg-vorpommern" xr:uid="{A99FDD0D-97E1-4EDC-A924-217A2542FAA4}"/>
+    <hyperlink ref="A10" r:id="rId15" display="https://www.ferienwiki.de/ferientermine/de/niedersachsen" xr:uid="{D74AFBDA-5E56-4792-9D96-1DA6F6183E8E}"/>
+    <hyperlink ref="A11" r:id="rId16" display="https://www.ferienwiki.de/ferientermine/de/nordrhein-westfalen" xr:uid="{10F9E5EE-F865-4C6D-999B-B38B3CE8785E}"/>
+    <hyperlink ref="A12" r:id="rId17" display="https://www.ferienwiki.de/ferientermine/de/rheinland-pfalz" xr:uid="{C4777859-69D9-4E6F-BF0C-65E4C380C865}"/>
+    <hyperlink ref="A13" r:id="rId18" display="https://www.ferienwiki.de/ferientermine/de/saarland" xr:uid="{B8CBD1DB-8750-479A-BE4B-DF4CB888251C}"/>
+    <hyperlink ref="A14" r:id="rId19" display="https://www.ferienwiki.de/ferientermine/de/sachsen" xr:uid="{A2D3E4FF-61FD-40D9-9075-3FCD530D69B2}"/>
+    <hyperlink ref="A15" r:id="rId20" display="https://www.ferienwiki.de/ferientermine/de/sachsen-anhalt" xr:uid="{8421A7A9-C500-4090-833D-B21EF72593E4}"/>
+    <hyperlink ref="A16" r:id="rId21" display="https://www.ferienwiki.de/ferientermine/de/schleswig-holstein" xr:uid="{21523797-C749-42AC-B734-6DBA15A894BE}"/>
+    <hyperlink ref="A17" r:id="rId22" display="https://www.ferienwiki.de/ferientermine/de/thueringen" xr:uid="{36C1EF35-3CCB-4357-A3C0-9D12528E899A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150BDF70-43D0-49A3-A12F-3A52A9C6D7BB}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="43.8" thickBot="1">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="23.4" thickBot="1">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="23.4" thickBot="1">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1">
+      <c r="A5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="23.4" thickBot="1">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1.02</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1">
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.8" thickBot="1">
+      <c r="A9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="6">
+        <v>11.06</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1">
+      <c r="A13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1">
+      <c r="A14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="4">
+        <v>31.05</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29.4" thickBot="1">
+      <c r="A16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="4">
+        <v>31.05</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1">
+      <c r="A17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="8">
+        <v>31.05</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B1" r:id="rId1" display="https://www.ferienwiki.de/ferientermine/2019/de/winterferien" xr:uid="{BE6EC636-A4B5-4DB6-8D96-752D5F110EFA}"/>
+    <hyperlink ref="C1" r:id="rId2" display="https://www.ferienwiki.de/ferientermine/2019/de/osterferien" xr:uid="{7C21B76C-E2C6-4E36-94DA-CB67ACA41CF6}"/>
+    <hyperlink ref="D1" r:id="rId3" display="https://www.ferienwiki.de/ferientermine/2019/de/pfingstferien" xr:uid="{EC9B9383-F3F7-4697-B921-8EB82DEFB08C}"/>
+    <hyperlink ref="E1" r:id="rId4" display="https://www.ferienwiki.de/ferientermine/2019/de/sommerferien" xr:uid="{6ED6BC06-ECA5-4097-BB89-862233006563}"/>
+    <hyperlink ref="F1" r:id="rId5" display="https://www.ferienwiki.de/ferientermine/2019/de/herbstferien" xr:uid="{0CEF3B4E-2CF8-4CFF-9B5E-1C703A6A346B}"/>
+    <hyperlink ref="G1" r:id="rId6" display="https://www.ferienwiki.de/ferientermine/2019/de/weihnachtsferien" xr:uid="{D6242EF0-BBD5-4849-A737-D0829715FC05}"/>
+    <hyperlink ref="A2" r:id="rId7" display="https://www.ferienwiki.de/ferientermine/de/baden-wuerttemberg" xr:uid="{C2004DB7-05F1-4D38-8BAE-B818D90FDDD5}"/>
+    <hyperlink ref="A3" r:id="rId8" display="https://www.ferienwiki.de/ferientermine/de/bayern" xr:uid="{A6D4B616-BC9E-4EC5-8F2C-015762781998}"/>
+    <hyperlink ref="A4" r:id="rId9" display="https://www.ferienwiki.de/ferientermine/de/berlin" xr:uid="{4A3845AE-3786-444A-9CE8-E00A413BF1A1}"/>
+    <hyperlink ref="A5" r:id="rId10" display="https://www.ferienwiki.de/ferientermine/de/brandenburg" xr:uid="{C6D15F84-B86D-4F10-A37C-B5DAECC92DF8}"/>
+    <hyperlink ref="A6" r:id="rId11" display="https://www.ferienwiki.de/ferientermine/de/bremen" xr:uid="{CC1AFD42-9504-43C1-89AD-120769238A58}"/>
+    <hyperlink ref="A7" r:id="rId12" display="https://www.ferienwiki.de/ferientermine/de/hamburg" xr:uid="{320B03E3-A7AD-4CCD-B843-B4545BA66E62}"/>
+    <hyperlink ref="A8" r:id="rId13" display="https://www.ferienwiki.de/ferientermine/de/hessen" xr:uid="{908E0CBB-0676-45BD-B9F3-56D713036D55}"/>
+    <hyperlink ref="A9" r:id="rId14" display="https://www.ferienwiki.de/ferientermine/de/mecklenburg-vorpommern" xr:uid="{7C706473-C501-423E-A29F-B675EC9F7CEC}"/>
+    <hyperlink ref="A10" r:id="rId15" display="https://www.ferienwiki.de/ferientermine/de/niedersachsen" xr:uid="{DD933170-7D99-493B-96AE-EB19513E3B4A}"/>
+    <hyperlink ref="A11" r:id="rId16" display="https://www.ferienwiki.de/ferientermine/de/nordrhein-westfalen" xr:uid="{0EE964B0-5EB8-41DC-BD90-36B2F7C52A81}"/>
+    <hyperlink ref="A12" r:id="rId17" display="https://www.ferienwiki.de/ferientermine/de/rheinland-pfalz" xr:uid="{5223D969-4605-4941-9765-D17B1B9F0DF9}"/>
+    <hyperlink ref="A13" r:id="rId18" display="https://www.ferienwiki.de/ferientermine/de/saarland" xr:uid="{AB32D2E5-946E-451D-A0E6-D48B9E4EBFAE}"/>
+    <hyperlink ref="A14" r:id="rId19" display="https://www.ferienwiki.de/ferientermine/de/sachsen" xr:uid="{2BD21F43-3F1A-4148-B616-9537B4BA4AC2}"/>
+    <hyperlink ref="A15" r:id="rId20" display="https://www.ferienwiki.de/ferientermine/de/sachsen-anhalt" xr:uid="{C3343103-CA88-46A7-905C-A1DAFD5ADE4E}"/>
+    <hyperlink ref="A16" r:id="rId21" display="https://www.ferienwiki.de/ferientermine/de/schleswig-holstein" xr:uid="{3C533D58-458D-411D-930E-81189A6A42CA}"/>
+    <hyperlink ref="A17" r:id="rId22" display="https://www.ferienwiki.de/ferientermine/de/thueringen" xr:uid="{3E95C9DB-301F-465C-A85B-14A5B25AC814}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
